--- a/important_mails_2026-07-11.xlsx
+++ b/important_mails_2026-07-11.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:H269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8002,7 +8002,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>KYC审核类</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -8017,73 +8017,21 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Wed, 10 Jun 2026 16:09:43 +0000</t>
+          <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (JKfyD/ypoS)</t>
+          <t>Seller News: June 2026</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-9762392-5679813
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1970326497550043</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>Seller News: June 2026</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -8100,39 +8048,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 14:39:15 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8149,39 +8097,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 10:10:03 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -8205,39 +8153,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 17:09:13 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Access your January–March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -8253,39 +8201,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 16:54:53 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Access your January - March 2026 China tax report</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -8301,39 +8249,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8353,39 +8301,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:43:29 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8402,39 +8350,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 14:42:06 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8454,39 +8402,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:21:30 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8506,39 +8454,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8555,39 +8503,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 03:31:27 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8607,39 +8555,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sun, 28 Jun 2026 03:28:55 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8659,39 +8607,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:38:10 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8708,39 +8656,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:37:54 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8760,39 +8708,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:52:57 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8809,39 +8757,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:51:45 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8861,39 +8809,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 13:45:52 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8913,39 +8861,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:12 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Updated China tax report link for October - December 2025</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  We’re resending your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -8963,39 +8911,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:05 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -9011,39 +8959,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:38 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9063,39 +9011,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 14:09:19 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9112,39 +9060,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 16:37:09 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>Estimado vendedor:
  Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 192.85 con el fin de saldar tu cuenta de vendedor de Amazon.
@@ -9156,39 +9104,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 14:05:42 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9208,39 +9156,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 12:44:57 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9257,39 +9205,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:50:33 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9309,39 +9257,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 13:23:55 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9358,39 +9306,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:11:15 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9410,39 +9358,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 13:09:47 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9459,39 +9407,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 17:21:56 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January–March 2026</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -9508,39 +9456,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 16:54:51 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -9557,39 +9505,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 08:40:50 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Envía el número de registro de España para la responsabilidad ampliada del productor con respecto a los RAEE a más tardar el 30 de septiembre</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Presenta el número de registro de la responsabilidad ampliada del productor a más tardar el 30 de septiembre o se te inscribirá automáticamente en RAP: Pago en mi nombre.
  96
@@ -9598,39 +9546,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 14:39:03 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9650,39 +9598,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:27:04 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9702,39 +9650,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:25:49 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9751,39 +9699,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:24:48 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9803,39 +9751,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 06:40:46 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Seller Central &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>重要信息：即刻重新验证您的所有 付款账户或存款方式</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
  亲爱的卖家，
@@ -9869,39 +9817,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:24:03 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9921,39 +9869,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 14:23:28 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -9970,39 +9918,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 13:35:44 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10022,39 +9970,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:28:40 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10074,39 +10022,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:24:36 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10123,39 +10071,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 13:24:04 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10175,39 +10123,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10227,39 +10175,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 12:54:19 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -10279,231 +10227,40 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 11 Jun 2026 15:13:12 +0000</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>Nieuregulowane saldo na koncie Amazon</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>Witamy!
- Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 42.71. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
- Jeśli ta karta ma limit kredytowy, możemy ją obciążać do momentu pełnej spłaty nieuregulowanego salda.
- Aby uzyskać więcej informacji, wyszukaj Dokonaj płatności w Pomocy Seller Central.
- Aby dowiedzieć się więcej na temat raportów płatności i Twoich działań, wyszukaj Wyświetl moje raporty o płatnościach w Pomocy Seller Central.
- Z poważaniem,
- Amazon Payments Europe SCA (société en commandite par actions) to spółka komandytowo-akcyjna zarejestrowana w Luksemburgu, numer rejestracyjny (RCS Luxembourg) B 153 265, z siedzibą pod adresem 38 avenue J.F. Kennedy, L-1855 Luxembourg. Numer VAT: LU 24448288. Amazon Payments Europe SCA posiada upoważnienie Komisji Nadzoru Sektora Finansowego w Luksemburgu do emisji pieniądza elektronicznego (numer licencji 36/10)
- Czy ten e-mail był pomocny?
- SPC-EUAmazon-1653667152334476</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 11 Jun 2026 11:53:43 +0000</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F191" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 06/11/26 11:53 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 518.07.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 11 Jun 2026 11:51:09 +0000</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 06/11/26 11:50 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 245,82.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 16:29:28 +0000</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;informacion-vendedor@amazon.mx&gt;</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>Pago del saldo en tu cuenta de pagos de Vender en Amazon</t>
-        </is>
-      </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>Estimado vendedor:
- Hemos realizado un cargo en tu tarjeta de crédito (Visa) por valor de MXN 90.75 con el fin de saldar tu cuenta de vendedor de Amazon.
- El monto cobrado puede ser inferior al total que debes si tu banco ha impuesto un límite de crédito. Si se da tal caso, seguiremos intentando realizar el cargo cada 24 horas en la tarjeta de crédito hasta que se haya pagado por completo el saldo deudor que presenta tu cuenta de vendedor de Amazon.
- También puedes utilizar la funcionalidad Hacer un pago para liquidar tu cuenta. Para más información, escribe "hacer un pago" en la barra de búsqueda de Seller Central.
- Para consultar tu historial de pagos, inicia sesión en tu cuenta y ve a Reportes &gt; Pagos.
- Gracias por vender en Amazon.
- SPC-USAmazon-1794405199581451</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 06:41:28 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -10518,39 +10275,39 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:09:44 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant is now live in France, Italy &amp; Spain</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  AI-powered assistance is now available in Seller Central to help you manage your business more efficiently.
@@ -10568,40 +10325,40 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 13:15:52 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>The Amazon Accelerate 2026 speaker lineup is here! Register now to
  save $100</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z49sbm/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
 [Speakers at Accelerate](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z49sbq/6744236849/h/wes7VJdAGIYNS4DfvXPWWwdvIH7_mIadF_Oxp_jSZW8)
@@ -10618,40 +10375,40 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 04:09:19 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -10663,40 +10420,40 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 04:08:32 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>"seller.service05@amazon.com" &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>[Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID 20858098381] *UPDATE* US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -10708,40 +10465,40 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 02:52:15 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -10760,39 +10517,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 12:40:58 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -10808,39 +10565,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:56:40 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -10866,39 +10623,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 08:39:22 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -10924,39 +10681,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:15:17 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -10965,39 +10722,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 04:34:37 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -11022,40 +10779,40 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 06:03:25 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -11073,40 +10830,40 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 19:23:07 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;seller.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20858098381] US - Food and Product Safety - ASIN:
  B0DD7R3PPG</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20858098381] US - Food and Product Safety - ASIN: B0DD7R3PPG
@@ -11131,39 +10888,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:11:59 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -11182,39 +10939,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:32 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -11233,39 +10990,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:09:28 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -11284,39 +11041,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:32:14 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>"pars-rp-core-sellerappeals-transfer@amazon.com" &lt;pars-rp-core-sellerappeals-transfer@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20516062511] 危险物品（危险品）</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20516062511] 危险物品（危险品）
@@ -11344,39 +11101,39 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:22 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -11395,39 +11152,39 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 20:37:03 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Important message: your account is at risk of deactivation</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>96
  96
@@ -11447,40 +11204,40 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Mon, 15 Jun 2026 06:46:26 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -11496,40 +11253,40 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 10:18:49 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -11556,39 +11313,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 03:03:53 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Review issue on FBA Shipment (FBA1234567)</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>96
  Review shipment defects to avoid reoccurrence
@@ -11608,40 +11365,40 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 13:54:53 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -11654,40 +11411,40 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 10:51:40 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -11706,236 +11463,39 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 11 Jun 2026 13:08:16 +0000</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F218" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Hello Weihai CA,
- Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
- To avoid further impact to your account, close or delete any non-compliant listings that you do </t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 11 Jun 2026 04:06:26 +0000</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
-        </is>
-      </c>
-      <c r="F219" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
- DOC REVIEW</t>
-        </is>
-      </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
-        <is>
-          <t>96
-SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
- Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-Upon review, we determined that the Safety Data Sheet ( SDS ) you uploaded for your ASIN is invalid due to it being incomplete, inaccurate, or otherwise conflicting, and thus, cannot be used for classification. Even though you've provided a written statement asserting that this SDS is the correct one, unfortunately, it doesn't validate its applicability for your product due to the following issues with the SDS:
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was create</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 19:04:36 +0000</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F220" s="2" t="inlineStr">
-        <is>
-          <t>New EU restriction on textile and footwear disposal</t>
-        </is>
-      </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
-        <is>
-          <t>96
- By July 19, update your removal settings for apparel, clothing and footwear in EU fulfillment centers
- Hello,
-Starting July 19, 2026 , new EU requirements under the Ecodesign for Sustainable Products Regulation (ESPR) will restrict the destruction of certain unsold products, including apparel, clothing accessories, and footwear.
- With this change, you may incur a fine for the disposal of these products in line with local country requirements, based on your business size and disposal volume.
-If you sell textiles or footwear in the EU, we recommend that you update your FBA removal settings to Return, Liquidate, or Donate (where eligible) before July 19, 2026.
-To review removal options and eligibility, go to Remove Inventory from a Fulfillment Center .
- Note: Products that aren’t eligible for donation or liquidation may require disposal in line with relevant regulations and safety guidelines. This may impact your ESPR compliance status.
-Also, on June 25, we’ll update the Fulfillment by Amazon (FBA) Donations terms and conditions in accordance with the above new requirement, our increased cross-border donation capabilities for inventory in Europe, and for program consistency.
-To le</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 18:11:21 +0000</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F221" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:26:45 +0000</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>El Asistente de vendedores ya está activo en Francia, Italia y España</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>96
  La asistencia con tecnología de IA ya está disponible en Seller Central para ayudarte a gestionar tu negocio de forma más eficiente.
@@ -11949,39 +11509,39 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 14:11:01 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -11999,39 +11559,39 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 13:49:18 +0000</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>L'assistente venditori è ora attivo in Francia, Italia e Spagna</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  L'assistenza basata su AI è ora disponibile in Seller Central per aiutarti a gestire la tua attività in modo più efficiente.
@@ -12046,39 +11606,39 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 16:04:35 +0000</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>Presentar información de cumplimiento normativo de la RAP en Portugal</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>96
  La normativa portuguesa sobre la RAP se aplica a los productos vendidos a clientes de Portugal.
@@ -12095,39 +11655,39 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 02:53:05 +0000</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 06/2026</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -12145,39 +11705,39 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Tue, 30 Jun 2026 00:26:34 +0000</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12929127032&lt;/p&gt;
@@ -12192,39 +11752,39 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Mon, 29 Jun 2026 14:10:24 +0000</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -12240,39 +11800,39 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:40:10 +0000</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -12287,39 +11847,39 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Fri, 26 Jun 2026 14:07:09 +0000</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -12347,39 +11907,39 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 22:31:41 +0000</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para julio</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para julio
@@ -12408,39 +11968,39 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 01:48:42 +0000</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Łącze do zaktualizowanego raportu podatkowego dotyczącego Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>96
  Ponownie przesyłamy kwartalny raport podatkowy, który obejmuje dane takie jak informacje o tożsamości, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -12458,39 +12018,39 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Wed, 24 Jun 2026 10:01:00 +0000</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -12509,39 +12069,39 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 16:59:26 +0000</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -12555,39 +12115,39 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Tue, 23 Jun 2026 00:26:49 +0000</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12908112692&lt;/p&gt;
@@ -12602,39 +12162,39 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Mon, 22 Jun 2026 09:29:52 +0000</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Prime会员日明天开始：最后提报促销活动的机会</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -12658,39 +12218,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Sun, 21 Jun 2026 12:49:43 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -12705,39 +12265,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 10:18:43 +0000</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -12758,39 +12318,39 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Fri, 19 Jun 2026 10:02:13 +0000</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>最后机会：请于6月19日前提报 Prime Day 促销</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -12813,39 +12373,39 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 14:18:31 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -12865,39 +12425,39 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 10:14:39 +0000</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>Soumettre les numéros d'enregistrement REP avant le 30 juin</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -12906,39 +12466,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>Thu, 18 Jun 2026 09:11:12 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>Seller News: June 2026</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -12958,40 +12518,40 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 17:13:19 +0000</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>Get increased New Selection Program (2026) benefits starting July
  30</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>96
  Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
@@ -13005,39 +12565,39 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>Wed, 17 Jun 2026 00:29:05 +0000</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12891299002&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Grazie per aver creato un nuovo caso: -- 12891299002&lt;/p&gt;
@@ -13053,39 +12613,39 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 14:26:46 +0000</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -13100,39 +12660,39 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:13:30 +0000</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -13149,39 +12709,39 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:12:43 +0000</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -13199,40 +12759,40 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:12:12 +0000</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -13250,39 +12810,39 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 11:08:19 +0000</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -13300,39 +12860,39 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:17:27 +0000</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -13371,39 +12931,39 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:16:32 +0000</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -13421,39 +12981,39 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:16:13 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, xiao jianming:
@@ -13471,40 +13031,40 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:15:21 +0000</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -13522,39 +13082,39 @@
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 10:13:24 +0000</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Documents de sécurité des produits requis pour les garder actifs</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour xiao jianming,
@@ -13572,39 +13132,39 @@
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Sun, 14 Jun 2026 13:34:40 +0000</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -13619,39 +13179,39 @@
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 17:10:30 +0000</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -13669,40 +13229,40 @@
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 04:55:50 +0000</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Hemos actualizado los requisitos del distintivo de Prime para Prime
  Day</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr"/>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>96
  Para ayudarte a mantener el distintivo de Prime durante Prime Day, hemos actualizado nuestros requisitos del distintivo en España.
@@ -13723,39 +13283,39 @@
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:49:02 +0000</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr"/>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -13777,39 +13337,39 @@
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:44:43 +0000</t>
         </is>
       </c>
-      <c r="E259" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F259" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr"/>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -13829,39 +13389,39 @@
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:35:25 +0000</t>
         </is>
       </c>
-      <c r="E260" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F260" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Mise à jour du statut des matières dangereuses (Hazmat)</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr"/>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>96
  Mise à jour du statut des matières dangereuses (Hazmat)
@@ -13873,39 +13433,39 @@
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:03:25 +0000</t>
         </is>
       </c>
-      <c r="E261" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F261" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr"/>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -13917,39 +13477,39 @@
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D262" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:03:17 +0000</t>
         </is>
       </c>
-      <c r="E262" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F262" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>Update van status gevaarlijke goederen</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr"/>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>96
  Update van status gevaarlijke goederen
@@ -13971,501 +13531,39 @@
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 11 Jun 2026 11:41:38 +0000</t>
-        </is>
-      </c>
-      <c r="E263" s="2" t="inlineStr">
-        <is>
-          <t>"Pereira, Sheryl" &lt;persher@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F263" s="2" t="inlineStr">
-        <is>
-          <t>Amazon India your next growth market</t>
-        </is>
-      </c>
-      <c r="G263" s="2" t="inlineStr"/>
-      <c r="H263" s="2" t="inlineStr">
-        <is>
-          <t>Hi Team,
-Sheryl this side from Amazon India Out of Country team, we work with high-potential global brands to successfully launch and scale their presence in India. Given the current selection gaps and growing customer demand, I believe Amazon.in could be a great opportunity for Roaxkois
-I'd love to connect for a brief discussion to walk you through the business potential and launch process. Let me know if you'd be open to a quick connect, you can also block my calendar with https://amazon.zoom.us/zbook/sheryl-pereira/sheryl-international-business-introductory-connect
-Looking forward to hearing from you!
-Regards,
-Sheryl Pereira
-Business Development Associate,
-Amazon Global Sales-India
-[cid:image002.png@01DCF9C5.1AD67C90]LinkedIn&lt;https://www.linkedin.com/in/sheryl-p/&gt;| International Brands Storefront&lt;https://www.amazon.in/gp/browse.html?node=21469514031&amp;ref_=nav_em_nav_ibrand_desktop_0_1_1_33&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 11 Jun 2026 08:25:43 +0000</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F264" s="2" t="inlineStr">
-        <is>
-          <t>最大化您的 Prime Day 业绩</t>
-        </is>
-      </c>
-      <c r="G264" s="2" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr">
-        <is>
-          <t>最大化您的 Prime Day 业绩
-尊敬的卖家，
-为 2026 年 Prime Day做好准备 - 为数百万 Prime 会员打造不容错过的优惠！加入我们今年6月为期4天活动。通过提交促销，确保充足库存，提升曝光度以助力您冲刺最佳业绩！
-关键日期
-活动日期： 2026年6月 (具体日期待公布)
-提报截止日期： 促销 – 2026 年 6 月 19 日，价格折扣 – 活动结束前 12 小时
-提报您的促销 &gt; https://go.amazonsellerservices.com/e/229492/reate-ld-DC-EM-D466345311-Wk24/7z3z1q7/6709636974/h/uq3xXX59LyOSLanIApIcx-STiI62BQPtDoy9SBDVxwA
-&lt;table align="center" border="0" cellpadding="0" cellspacing="0" class="section" role="presentation" style="width:100%;"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td align="center"&gt;
-			&lt;div role="none"&gt;
-&lt;!--[if(mso)|(IE)]&gt;
-&lt;table align="center" border="0" cellpadding="0" cellspacing="0" class="block-grid-outlook" style="width:600px;" width="600" &gt;
-&lt;tr&gt;
-&lt;td style="line-height:0px;font-size:0px;mso-line-height-rule:exactly;"&gt;&lt;![endif]--&gt;
-			&lt;div style="margin:0 auto;border-radius:0px;max-width:600px;"&gt;
-			&lt;table align="center" border="0" cellpadding="0" cellspacing="0" role="presentation" style="width:100%;border-radius:0px;"&gt;
-				&lt;tbody&gt;
-					&lt;tr&gt;
-						&lt;td class="block-grid" style="border-radius:0px;font-size:0px;padding:12px 0px 12px 0px;text-align:center;vertical-align:top;"&gt;
-&lt;!--[if(mso)|(IE)]&gt;
-&lt;table role="presentation" border="0" cellpadding="0" cellspacing</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 20:16:28 +0000</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F265" s="2" t="inlineStr">
-        <is>
-          <t>27 lipca rozpocznie się ulepszanie tytułów stron produktów</t>
-        </is>
-      </c>
-      <c r="G265" s="2" t="inlineStr"/>
-      <c r="H265" s="2" t="inlineStr">
-        <is>
-          <t>96
- Tytuły we wszystkich kategoriach (z wyjątkiem kategorii „Media”) będą musiały zawierać 75 znaków lub mniej, łącznie ze spacjami. Nowa funkcja „Najważniejsze informacje” zapewnia dodatkowe 125 znaków, umożliwiając udostępnianie materiałów.
- Dzień dobry,
- tytuły stron produktów są jedną z pierwszych rzeczy, które widzą klienci, a dla klientów kupujących przy użyciu urządzeń mobilnych liczy się każdy znak. Aby zagwarantować, że tytuły stron produktów są atrakcyjne dla klientów na całym świecie, wprowadzamy pewne zmiany, które pomogą Ci z łatwością przedstawić nazwę produktu i najważniejsze informacje o nim.
- Począwszy od 27 lipca 2026 r. tytuły we wszystkich kategoriach (z wyjątkiem kategorii „Media”) będą musiały zawierać 75 znaków lub mniej, łącznie ze spacjami. Zagwarantuje to, że tytuł będzie wyświetlany w całości na urządzeniach mobilnych i będzie zgodny z długością tytułów w innych sklepach internetowych.
- Najważniejsze informacje zawierają dodatkowe 125 znaków, aby umożliwić udostępnianie materiałów lub zalecanych zastosowań, które pomogą klientom porównać dostępne opcje. Treść ta jest możliwa do wyszukania oraz widoczna pod tytułami w wynikach wyszukiwania i na stronach pr</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 20:08:24 +0000</t>
-        </is>
-      </c>
-      <c r="E266" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F266" s="2" t="inlineStr">
-        <is>
-          <t>Aggiornamenti per migliorare i titoli dei prodotti a partire dal 27
- luglio</t>
-        </is>
-      </c>
-      <c r="G266" s="2" t="inlineStr"/>
-      <c r="H266" s="2" t="inlineStr">
-        <is>
-          <t>96
- I titoli in tutte le categorie eccetto i prodotti multimediali dovranno contenere un massimo di 75 caratteri, spazi inclusi. Nelle caratteristiche principali dei prodotti, saranno ora disponibili altri 125 caratteri per descrivere i materiali.
- Buongiorno,
- i titoli dei prodotti sono una delle prime cose che i clienti vedono e, per i clienti che effettuano acquisti su dispositivi mobili, ogni carattere è importante. Per fare in modo che i titoli dei prodotti attirino clienti di tutto il mondo, abbiamo apportato delle modifiche che ti aiuteranno a mostrare il nome e le caratteristiche principali dei prodotti in modo uniforme.
- A partire dal 27 luglio 2026 , i titoli in tutte le categorie eccetto i prodotti multimediali dovranno contenere un massimo di 75 caratteri, spazi inclusi. Questo assicurerà che il titolo venga visualizzato completamente sul dispositivo mobile e sia coerente con la lunghezza usata da altri negozi online.
- Per le caratteristiche principali dell'articolo, saranno disponibili altri 125 caratteri per descrivere i materiali o i casi d'uso consigliati, in modo da consentire ai clienti di confrontare le opzioni. Questi contenuti saranno ricercabili e visibili sot</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D267" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 20:05:34 +0000</t>
-        </is>
-      </c>
-      <c r="E267" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F267" s="2" t="inlineStr">
-        <is>
-          <t>Updates om je producttitels te verbeteren beginnen op 27 juli</t>
-        </is>
-      </c>
-      <c r="G267" s="2" t="inlineStr"/>
-      <c r="H267" s="2" t="inlineStr">
-        <is>
-          <t>96
- Titels in alle categorieën, behalve in de categorie ‘media’ mogen maximaal 75 tekens lang zijn, inclusief spaties. Met de nieuwe functie Itemhoogtepunten kun je nu 125 extra tekens gebruiken om materiaal te delen.
- Hallo,
- Je producttitels zijn een van de eerste dingen die klanten zien, en voor klanten die mobiel winkelen, telt elk teken. Om ervoor te zorgen dat je producttitels overal klanten aanspreken, voeren we een aantal wijzigingen door waarmee je je productnaam en de belangrijkste kenmerken van je product naadloos kunt weergeven.
- Vanaf 27 juli 2026 mogen titels in alle categorieën, behalve in de categorie ‘media’, maximaal 75 tekens lang zijn, inclusief spaties. Dit zorgt ervoor dat je titel volledig wordt weergegeven op mobiel en overeenkomt met de titellengte die door andere online winkels wordt gebruikt.
- Itemhoogtepunten bevatten 125 extra tekens voor het delen van materiaal of aanbevolen gebruikscases waarmee klanten opties kunnen vergelijken. Deze inhoud is zoekbaar en zichtbaar onder titels in zoekresultaten en op productpagina's.
- We bieden je tools die door AI worden aangedreven om ervoor te zorgen dat je nieuwe titels en itemhoogtepunten optimaal zijn. Je kunt</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 20:05:16 +0000</t>
-        </is>
-      </c>
-      <c r="E268" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F268" s="2" t="inlineStr">
-        <is>
-          <t>Las actualizaciones para mejorar los títulos de los productos entrarán en vigor el 27 de julio</t>
-        </is>
-      </c>
-      <c r="G268" s="2" t="inlineStr"/>
-      <c r="H268" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Los títulos de todas las categorías, excepto multimedia, tendrán que tener 75 caracteres o menos, contando espacios. La nueva herramienta de aspectos destacados del producto ahora ofrece 125 caracteres más para compartir materiales.
- Hola:
- Los títulos de los productos son uno de los primeros aspectos que ven los clientes y, para aquellos que compran en dispositivos móviles, cada carácter cuenta. Para garantizar que los títulos atraigan a clientes de todo el mundo, hemos hecho algunos cambios que te ayudarán a mostrar el nombre del producto y sus aspectos más destacados a la perfección.
- A partir del 27 de julio de 2026 , los títulos de todas las categorías, excepto multimedia, tendrán que tener 75 caracteres o menos, contando espacios. Así nos aseguramos de que el título se mostrará completamente en dispositivos móviles y que coincida con la longitud que utilizan otras tiendas en Internet.
- Los aspectos destacados del producto proporcionan 125 caracteres adicionales para dar información sobre materiales o casos de uso recomendados, lo que ayuda a los clientes a comparar opciones. Este contenido se puede buscar y aparece debajo de los títulos en los resultados de búsqueda, así </t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 19:10:59 +0000</t>
-        </is>
-      </c>
-      <c r="E269" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F269" s="2" t="inlineStr">
-        <is>
-          <t>Nueva restricción de la UE sobre la puesta de inventario de productos textiles y calzado a disposición de Amazon</t>
-        </is>
-      </c>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr">
-        <is>
-          <t>96
- A más tardar el 19 de julio, actualiza la configuración de retiradas de prendas de vestir y calzado en los centros logísticos de la UE
- Hola:
-A partir del 19 de julio de 2026 , los nuevos requisitos de la UE establecidos en el Reglamento sobre diseño ecológico de productos sostenibles restringirán la destrucción de determinados productos no vendidos, entre los que se incluyen prendas de vestir, complementos de moda y calzado.
- Con este cambio, podrías incurrir en una multa por la puesta de estos productos a nuestra disposición de acuerdo con los requisitos nacionales del país, en función del tamaño de tu empresa y del volumen de productos afectados.
-Si vendes productos textiles o calzado en la UE, te recomendamos que actualices la configuración de las retiradas de inventario de Logística de Amazon a "Devolver", "Liquidar" o "Donar" (cuando sea posible) antes del 19 de julio de 2026.
-Para consultar las opciones y requisitos de las retiradas, ve a Retirada de inventario de un centro logístico .
- Nota: Los productos que no puedan destinarse a donación o liquidación pueden requerir su puesta de inventario a disposición de Amazon de acuerdo con las normativas y directrices de seguri</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 19:03:48 +0000</t>
-        </is>
-      </c>
-      <c r="E270" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F270" s="2" t="inlineStr">
-        <is>
-          <t>Nuove limitazioni dell'Unione europea sul reimpiego di prodotti
- tessili e calzature</t>
-        </is>
-      </c>
-      <c r="G270" s="2" t="inlineStr"/>
-      <c r="H270" s="2" t="inlineStr">
-        <is>
-          <t>96
- Aggiorna le impostazioni di rimozione per capi di abbigliamento, accessori e calzature nei centri logistici dell'Unione europea entro il 19 luglio
- Buongiorno,
-a partire dal 19 luglio 2026 , i nuovi requisiti dell'Unione europea previsti dalle normative di progettazione ecocompatibile per prodotti sostenibili (ESPR) stabiliranno dei limiti alla distruzione di alcuni prodotti invenduti, tra cui abbigliamento, accessori e calzature.
- Di conseguenza, la distruzione di tali prodotti potrebbe esporti al rischio di multe, in base ai requisiti locali, alle dimensioni della tua attività e al volume di articoli distrutti.
-Se vendi prodotti tessili o calzature nell'Unione europea, ti consigliamo di aggiornare le impostazioni di rimozione di Logistica di Amazon su Restituzione, Liquidazione o Donazione (ove disponibili) entro il 19 luglio 2026.
-Per verificare le opzioni di rimozione e l'idoneità, consulta Rimuovere l'inventario da un centro logistico .
- Nota: I prodotti non idonei alla donazione o alla liquidazione potrebbero richiedere il reimpiego da parte di Amazon in conformità alle normative pertinenti e alle linee guida sulla sicurezza. Ciò potrebbe influire sullo stato di conformit</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 18:26:32 +0000</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F271" s="2" t="inlineStr">
-        <is>
-          <t>Nowe ograniczenia UE dotyczące usuwania tekstyliów i obuwia</t>
-        </is>
-      </c>
-      <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Do 19 lipca zmień ustawienia wycofywania zapasów odzieży i obuwia magazynowanych w centrach logistycznych w UE
- Dzień dobry,
-od 19 lipca 2026 r. możliwość niszczenia niektórych niesprzedanych produktów, w tym odzieży, akcesoriów odzieżowych i obuwia, zostanie ograniczona. Wynika to z nowych wymogów UE ustanowionych w rozporządzeniu w sprawie ekoprojektu dla zrównoważonych produktów (ESPR) .
- W związku z tą zmianą możesz otrzymać karę za usunięcie takich produktów zgodnie z wymogami danego kraju. Będzie ona zależeć od wielkości Twojego biznesu i usuwanych ilości.
-Jeśli prowadzisz sprzedaż tekstyliów lub obuwia w UE, przed 19 lipca 2026 r. zmień ustawienia wycofywania zapasów FBA na „Zwrot”, „Likwidacja” lub „Darowizna” (o ile opcja ta jest dostępna).
-Aby poznać opcje wycofywania i warunki kwalifikacji, przejdź na stronę Wycofywanie zapasów z centrum logistycznego .
- Uwaga: Produkty, które nie kwalifikują się do likwidacji ani do przekazania jako darowizna, mogą wymagać usunięcia zgodnie z odpowiednimi przepisami i wytycznymi dotyczącymi bezpieczeństwa. Może to wpłynąć na Twoją zgodność z rozporządzeniem ESPR.
-Ponadto 25 czerwca aktualizujemy warunki programu „Darowizny w ramach </t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 18:08:34 +0000</t>
-        </is>
-      </c>
-      <c r="E272" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F272" s="2" t="inlineStr">
-        <is>
-          <t>Nouvelle restriction de l’UE sur la mise au rebut des textiles et des chaussures</t>
-        </is>
-      </c>
-      <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr">
-        <is>
-          <t>96
- D’ici le 19 juillet, mettez à jour vos paramètres de demande de prélèvement pour les vêtements, les accessoires vestimentaires et les chaussures dans les centres de distribution de l’UE
- Bonjour,
-À partir du 19 juillet 2026 , de nouvelles exigences de l’UE prévues par le Règlement sur l’écoconception des produits durables (ESPR) limiteront la destruction de certains produits invendus, notamment les vêtements, les accessoires vestimentaires et les chaussures.
- Avec ce changement, vous risquez une amende pour la mise au rebut de ces produits conformément aux exigences locales, selon la taille de votre entreprise et le volume de mise au rebut.
-Si vous vendez des textiles ou des chaussures dans l’UE, nous vous recommandons de mettre à jour vos paramètres de prélèvement Expédié par Amazon sur Retour, Liquider ou Faire un don (si applicable) avant le 19 juillet 2026.
-Pour consulter les options de prélèvement et l’éligibilité, accédez à Prélever le stock d’un centre de distribution .
- Remarque : Les produits qui ne sont pas éligibles à un don ou à la liquidation peuvent nécessiter une mise au rebut conformément à la réglementation et aux instructions de sécurité applicables. Cela peut</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 04:34:30 +0000</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14489,39 +13587,39 @@
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:35:02 +0000</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14544,39 +13642,39 @@
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>Sat, 4 Jul 2026 03:23:13 +0000</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F275" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-16</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14597,39 +13695,39 @@
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:46:44 +0000</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14653,39 +13751,39 @@
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" s="2" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B277" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D277" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 04:45:39 +0000</t>
         </is>
       </c>
-      <c r="E277" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F277" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G277" s="2" t="inlineStr"/>
-      <c r="H277" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14709,39 +13807,39 @@
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B278" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D278" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>Sat, 27 Jun 2026 03:25:54 +0000</t>
         </is>
       </c>
-      <c r="E278" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F278" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-09</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr"/>
-      <c r="H278" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14763,39 +13861,39 @@
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B279" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 04:59:29 +0000</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F279" s="2" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr"/>
-      <c r="H279" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14819,39 +13917,39 @@
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B280" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
         <is>
           <t>Sat, 20 Jun 2026 03:24:34 +0000</t>
         </is>
       </c>
-      <c r="E280" s="2" t="inlineStr">
+      <c r="E261" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F280" s="2" t="inlineStr">
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-07-02</t>
         </is>
       </c>
-      <c r="G280" s="2" t="inlineStr"/>
-      <c r="H280" s="2" t="inlineStr">
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14873,39 +13971,39 @@
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B281" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D281" s="2" t="inlineStr">
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 04:57:38 +0000</t>
         </is>
       </c>
-      <c r="E281" s="2" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F281" s="2" t="inlineStr">
+      <c r="F262" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-25</t>
         </is>
       </c>
-      <c r="G281" s="2" t="inlineStr"/>
-      <c r="H281" s="2" t="inlineStr">
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14927,39 +14025,39 @@
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B282" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>Sat, 13 Jun 2026 04:53:34 +0000</t>
         </is>
       </c>
-      <c r="E282" s="2" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F282" s="2" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-25</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr"/>
-      <c r="H282" s="2" t="inlineStr">
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14983,39 +14081,39 @@
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B283" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D283" s="2" t="inlineStr">
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 00:16:50 +0000</t>
         </is>
       </c>
-      <c r="E283" s="2" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F283" s="2" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr"/>
-      <c r="H283" s="2" t="inlineStr">
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
@@ -15045,39 +14143,39 @@
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B284" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D284" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
         <is>
           <t>Thu, 25 Jun 2026 12:14:25 +0000</t>
         </is>
       </c>
-      <c r="E284" s="2" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F284" s="2" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>Connect with an Amazon expert at Seller Café—Save $100 with early-bird pricing</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr"/>
-      <c r="H284" s="2" t="inlineStr">
+      <c r="G265" s="2" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EM/7z46y96/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/4uHYwMZ-ld-EM/7z46y99/6733799304/h/qLPgz01lmZlp6bu7C295K13RXyMwFkd7KKOkI6IliSc)
@@ -15093,39 +14191,39 @@
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="2" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B285" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C285" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D285" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>Tue, 16 Jun 2026 03:04:08 +0000</t>
         </is>
       </c>
-      <c r="E285" s="2" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F285" s="2" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>Action Required: Transparency Barcode Required for Your Products</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr"/>
-      <c r="H285" s="2" t="inlineStr">
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello from Amazon Seller Services,
@@ -15141,39 +14239,39 @@
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B286" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D286" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 08:49:28 +0000</t>
         </is>
       </c>
-      <c r="E286" s="2" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>"Gao, Mark" &lt;gaomark@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F286" s="2" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>亚马逊广告限时激励活动 - Weihai EU</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr"/>
-      <c r="H286" s="2" t="inlineStr">
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>Amazon has replaced the attachment in this email with download link.
 Important: This link may contain content that is confidential. Please exercise appropriate caution when sharing.
@@ -15201,39 +14299,39 @@
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B287" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D287" s="2" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:43:31 +0000</t>
         </is>
       </c>
-      <c r="E287" s="2" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F287" s="2" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr"/>
-      <c r="H287" s="2" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -15255,39 +14353,39 @@
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B288" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D288" s="2" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>Fri, 12 Jun 2026 01:43:28 +0000</t>
         </is>
       </c>
-      <c r="E288" s="2" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F288" s="2" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr"/>
-      <c r="H288" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -15309,223 +14407,6 @@
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B289" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D289" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 11 Jun 2026 11:03:54 +0000</t>
-        </is>
-      </c>
-      <c r="E289" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F289" s="2" t="inlineStr">
-        <is>
-          <t>You have until July 17 to verify FBA dimensions for fee calculation</t>
-        </is>
-      </c>
-      <c r="G289" s="2" t="inlineStr"/>
-      <c r="H289" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
- 96
- As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
-                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ </t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B290" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D290" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 20:33:42 +0000</t>
-        </is>
-      </c>
-      <c r="E290" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F290" s="2" t="inlineStr">
-        <is>
-          <t>Updates to improve your product titles begin on July 27</t>
-        </is>
-      </c>
-      <c r="G290" s="2" t="inlineStr"/>
-      <c r="H290" s="2" t="inlineStr">
-        <is>
-          <t>96
- Titles in all categories except for media will need to be 75 characters or less including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
- Hello,
- Your product titles are one of the first things customers see, and for customers shopping on mobile, every character counts. To ensure your product titles appeal to customers everywhere, we’re making some changes that will help you show your product name and your product highlights seamlessly.
- Starting July 27, 2026 , titles in all categories except for media will need to be 75 characters or less including spaces. This ensures that your title will fully display in mobile and is consistent with the title length used by other online stores.
- Item Highlights provides an additional 125 characters for sharing materials or recommended use cases that help customers compare options. This content is searchable and visible below titles in search results and on product detail pages.
- We’re providing you with AI-powered tools to ensure that your new titles and Item Highlights are optimal. You can start reviewing, modifying, and using AI-recommended titles and Item Highlights today by taking</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B291" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C291" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D291" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 20:07:52 +0000</t>
-        </is>
-      </c>
-      <c r="E291" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F291" s="2" t="inlineStr">
-        <is>
-          <t>Updates to improve your product titles begin on July 27</t>
-        </is>
-      </c>
-      <c r="G291" s="2" t="inlineStr"/>
-      <c r="H291" s="2" t="inlineStr">
-        <is>
-          <t>96
- Titles in all categories except media will need to be 75 characters or less, including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
- Hello,
- Your product titles are one of the first things that customers see, and for customers shopping on mobile, every character counts. To ensure that your product titles appeal to customers everywhere, we’re making some changes that will help you show your product name and your product highlights seamlessly.
- Starting from July 27, 2026 , titles in all categories except media will need to be 75 characters or less, including spaces. This ensures that your title will fully display on mobile devices and is consistent with the title length used by other online stores.
- Item Highlights provides an additional 125 characters for sharing materials or recommended use cases that help customers compare options. This content is searchable and visible below titles in search results and on product detail pages.
- We’re providing you with AI-powered tools to ensure that your new titles and Item Highlights are optimal. You can start reviewing, modifying and using AI-recommended titles and Item Highlights</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B292" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C292" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D292" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 20:04:50 +0000</t>
-        </is>
-      </c>
-      <c r="E292" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F292" s="2" t="inlineStr">
-        <is>
-          <t>Updates to improve your product titles begin on July 27</t>
-        </is>
-      </c>
-      <c r="G292" s="2" t="inlineStr"/>
-      <c r="H292" s="2" t="inlineStr">
-        <is>
-          <t>96
- Titles in all categories except for media will need to be 75 characters or less including spaces. A new Item Highlights feature now provides an additional 125 characters for sharing materials.
- Hello,
- Your product titles are one of the first things customers see, and for customers shopping on mobile, every character counts. To ensure your product titles appeal to customers everywhere, we’re making some changes that will help you show your product name and your product highlights seamlessly.
- Starting July 27, 2026 , titles in all categories except for media will need to be 75 characters or less including spaces. This ensures that your title will fully display in mobile and is consistent with the title length used by other online stores.
- Item Highlights provides an additional 125 characters for sharing materials or recommended use cases that help customers compare options. This content is searchable and visible below titles in search results and on product detail pages.
- We’re providing you with AI-powered tools to ensure that your new titles and Item Highlights are optimal. You can start reviewing, modifying, and using AI-recommended titles and Item Highlights today by taking</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B293" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C293" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D293" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 10 Jun 2026 19:18:13 +0000</t>
-        </is>
-      </c>
-      <c r="E293" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F293" s="2" t="inlineStr">
-        <is>
-          <t>Updates to improve your product titles begin on July 27</t>
-        </is>
-      </c>
-      <c r="G293" s="2" t="inlineStr"/>
-      <c r="H293" s="2" t="inlineStr">
-        <is>
-          <t>96
- Titles in all categories except for media will need to be 75 characters or less, including spaces. A new item highlights feature now provides an additional 125 characters for sharing materials.
- Hello,
- Your product titles are one of the first things customers see and for customers shopping on mobile, every character counts. To ensure your product titles appeal to customers everywhere, we’re making some changes that will help you show your product name and your product highlights seamlessly.
- Starting July 27, 2026 , titles in all categories except for media will need to be 75 characters or less, including spaces. This ensures that your title will fully display in mobile and is consistent with the title length used by other online stores.
- Item highlights provides an additional 125 characters for sharing materials or recommended use cases that help customers compare options. This content is searchable and visible below titles in search results and on product detail pages.
- We’re providing you with AI-powered tools to ensure that your new titles and item highlights are optimal. You can start reviewing, modifying and using AI-recommended titles and item highlights today by taking</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
